--- a/02-Manual/Final-Testcases-excelsheet-Htu .xlsx
+++ b/02-Manual/Final-Testcases-excelsheet-Htu .xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alkhateeb/Desktop/Final-HTU/Manual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alkhateeb/Desktop/Final-HTU/02-Manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7344FEA2-93FD-D54D-905C-3F5A7DB62FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4758AE9-6C02-1147-A44A-41251723653A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" xr2:uid="{0ACC5647-8175-1A4D-98D6-EC920C24D7D6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" activeTab="2" xr2:uid="{0ACC5647-8175-1A4D-98D6-EC920C24D7D6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="343">
   <si>
     <t xml:space="preserve"> Test ID</t>
   </si>
@@ -88,9 +88,6 @@
     <t>username:locked_out_user /pass: secret_sauce</t>
   </si>
   <si>
-    <t>https://url-shortener.me/797V</t>
-  </si>
-  <si>
     <t>Login with problem user</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
   </si>
   <si>
     <t>pass</t>
-  </si>
-  <si>
-    <t>https://url-shortener.me/79LW</t>
   </si>
   <si>
     <t>Login should fail with error message</t>
@@ -170,9 +164,6 @@
 Password: secret_sauce</t>
   </si>
   <si>
-    <t>https://h7.cl/1hIBm</t>
-  </si>
-  <si>
     <t>Login with empty credentials</t>
   </si>
   <si>
@@ -187,9 +178,6 @@
   </si>
   <si>
     <t>Error message displayed: “Username is required”</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1hIB-</t>
   </si>
   <si>
     <t>Inventory page loaded and products displayed</t>
@@ -244,9 +232,6 @@
     <t xml:space="preserve">Pass	</t>
   </si>
   <si>
-    <t>https://2cm.es/1mWDb</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dropdown Arrow Click Functionality	</t>
   </si>
   <si>
@@ -271,9 +256,6 @@
     <t xml:space="preserve">Products sorted by price ascending	</t>
   </si>
   <si>
-    <t>https://2cm.es/1mWKk</t>
-  </si>
-  <si>
     <t>Verify adding product to shopping cart</t>
   </si>
   <si>
@@ -302,9 +284,6 @@
   </si>
   <si>
     <t xml:space="preserve">Both products displayed correctly	 </t>
-  </si>
-  <si>
-    <t>https://2cm.es/1mWTM</t>
   </si>
   <si>
     <t xml:space="preserve">Checkout - Valid Information	</t>
@@ -337,9 +316,6 @@
     <t xml:space="preserve">Error message displayed	</t>
   </si>
   <si>
-    <t>https://2cm.es/1mWVi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Checkout - Missing Postal Code	</t>
   </si>
   <si>
@@ -355,9 +331,6 @@
     <t xml:space="preserve">Error: "Postal Code is required"	</t>
   </si>
   <si>
-    <t>https://2cm.es/1mWYU</t>
-  </si>
-  <si>
     <t xml:space="preserve">Empty Cart Checkout	</t>
   </si>
   <si>
@@ -437,27 +410,15 @@
     <t xml:space="preserve">Redirected correctly	</t>
   </si>
   <si>
-    <t>https://2cm.es/1hZgN</t>
-  </si>
-  <si>
     <t>Privacy Policy Link</t>
   </si>
   <si>
     <t xml:space="preserve">     </t>
   </si>
   <si>
-    <t>https://2cm.es/1h-1p</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1ibkI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remove Item	</t>
   </si>
   <si>
-    <t>https://h7.cl/1naGm</t>
-  </si>
-  <si>
     <t>Verify item can be removed from cart</t>
   </si>
   <si>
@@ -479,9 +440,6 @@
     <t>Not all items can be added</t>
   </si>
   <si>
-    <t>https://h7.cl/1ibp-</t>
-  </si>
-  <si>
     <t>Sort products Z–A</t>
   </si>
   <si>
@@ -489,9 +447,6 @@
   </si>
   <si>
     <t>Products are sorted alphabetically from Z to A</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1ibs0</t>
   </si>
   <si>
     <t>Verify Checkout Information Input</t>
@@ -530,9 +485,6 @@
 3.Click Logout</t>
   </si>
   <si>
-    <t>https://h7.cl/1ibBE</t>
-  </si>
-  <si>
     <t>Login successful with expected delay</t>
   </si>
   <si>
@@ -561,15 +513,9 @@
     <t>Cart page opens</t>
   </si>
   <si>
-    <t>https://h7.cl/1ndkg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cart page opens </t>
   </si>
   <si>
-    <t>https://h7.cl/1idXw</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remove from Cart	</t>
   </si>
   <si>
@@ -579,9 +525,6 @@
     <t>Item removed</t>
   </si>
   <si>
-    <t>https://h7.cl/1ie1n</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sort Price Low-High	</t>
   </si>
   <si>
@@ -589,9 +532,6 @@
   </si>
   <si>
     <t>Products sorted by price ascending</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1ndrF</t>
   </si>
   <si>
     <t>Inventory images load</t>
@@ -624,9 +564,6 @@
     <t>User logged out successfully</t>
   </si>
   <si>
-    <t>https://h7.cl/1ndyB</t>
-  </si>
-  <si>
     <t>Product Images</t>
   </si>
   <si>
@@ -634,9 +571,6 @@
   </si>
   <si>
     <t>Each product shows unique image</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1ieb-</t>
   </si>
   <si>
     <t>Add to Cart</t>
@@ -649,9 +583,6 @@
     <t>Some items fail to add</t>
   </si>
   <si>
-    <t>https://h7.cl/1iedE</t>
-  </si>
-  <si>
     <t>Remove from Cart</t>
   </si>
   <si>
@@ -659,9 +590,6 @@
   </si>
   <si>
     <t>Items removed successfully</t>
-  </si>
-  <si>
-    <t>https://h7.cl/1ndE3</t>
   </si>
   <si>
     <t>Sort Price Low-High</t>
@@ -672,26 +600,14 @@
 3. Select “Price (low to high)”</t>
   </si>
   <si>
-    <t>https://h7.cl/1ieh-</t>
-  </si>
-  <si>
     <t>Login with standard username</t>
-  </si>
-  <si>
-    <t>https://rb.gy/hrz52s</t>
   </si>
   <si>
     <t>1. Login 
 2. Sort "Name (Z to A)" from sort dropdown</t>
   </si>
   <si>
-    <t>https://2cm.es/1o22Y</t>
-  </si>
-  <si>
     <t>Verify removing product from cart</t>
-  </si>
-  <si>
-    <t>https://2cm.es/1j06A</t>
   </si>
   <si>
     <t>1. Login 
@@ -719,9 +635,6 @@
 2. Select "Price (low to high)" from sort dropdown</t>
   </si>
   <si>
-    <t>https://2cm.es/1j0As</t>
-  </si>
-  <si>
     <t>1.Login                                         2. navigate to cart page
 3. Checkout
 4. Enter info
@@ -729,19 +642,7 @@
 6. Finish</t>
   </si>
   <si>
-    <t>https://2cm.es/1j2lc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Username:standard_user /pass: secret_sauce.         </t>
-  </si>
-  <si>
-    <t>https://2cm.es/1o4pB</t>
-  </si>
-  <si>
-    <t>https://2cm.es/1o4pW</t>
-  </si>
-  <si>
-    <t>https://2cm.es/1j2m-</t>
   </si>
   <si>
     <t>1. Login
@@ -762,9 +663,6 @@
     <t>Verify Privacy Policy link exists in footer and navigates to correct page</t>
   </si>
   <si>
-    <t>https://2cm.es/1o4VS</t>
-  </si>
-  <si>
     <t>1. Login 
 2. Go to inventory page</t>
   </si>
@@ -828,9 +726,6 @@
     <t>1. Navigate to login page  2. Enter credentials              3. Click "Login" button         4. Observe time until inventory page loads</t>
   </si>
   <si>
-    <t>https://2cm.es/1j360</t>
-  </si>
-  <si>
     <t>Significant delay (several seconds) before page loads Poor user experience</t>
   </si>
   <si>
@@ -911,12 +806,6 @@
     <t>Username: performance_glitch_user             Password: secret_sauce          First: Asad, Last: Ahmad, ZIP: 12345</t>
   </si>
   <si>
-    <t>https://2cm.es/1j3cl</t>
-  </si>
-  <si>
-    <t>https://2cm.es/1o5iB</t>
-  </si>
-  <si>
     <t>1. Login 
 2. Open products page
 3. Observe all product images</t>
@@ -934,9 +823,6 @@
   </si>
   <si>
     <t>User successfully logged in and redirected to inventory.html</t>
-  </si>
-  <si>
-    <t>https://2cm.es/1o5ki</t>
   </si>
   <si>
     <t>Category</t>
@@ -1135,9 +1021,6 @@
     <t>Cart empties , cart badge shows , but "Remove" buttons stay unchanged. Buttons only reset after manual page refresh or navigation.</t>
   </si>
   <si>
-    <t>https://2cm.es/1jbmn</t>
-  </si>
-  <si>
     <t>BR-008</t>
   </si>
   <si>
@@ -1164,17 +1047,137 @@
     <t xml:space="preserve">Privacy Policy text displays in footer as plain text (not a link). Text is not clickable. No navigation occurs when clicked. </t>
   </si>
   <si>
-    <t>https://2cm.es/1jc7P</t>
-  </si>
-  <si>
     <t>Multiple sorting operations ( ex:Price Low-High) fail to execute properly, with error messages indicating system-level failures reported to backend monitoring (Backtrace).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JTp-Cv0vUHQ7zYggxgLnpsyBx--nJAVl/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GyuPYfd765ynCWC0wopn-XdIpafwf87Q/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XlUg43XjgZfus-m4i5ZN51zPPJkX5YSg/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YW9Sp-l_EogBqe0_uexf_01EcBlvPk7F/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KR52SjzeqeA_RIfpWPxlnwy8b8tdBpay/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CmKUYYSgvmByeZpyjoYmPe1MJk-qq4sG/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VCkxrzmyHqwfP2QjUBFKVv4xTOKp6KUH/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kR9GDoMnfl67CWCldo3rboA8pWs47fYX/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-TZ7fczqf4RoE5VwqOSBaF_gfHgWhuTM/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZU-Ig8l2yv4ZL4h_dz1NUa4hODy4mJ8T/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16qrrzPuCA3PMdgbaFl5l0ZS83oobyZPb/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10pW5bFC8aTWW-w9v9svCo0i7Biag1X4f/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_ODJ9Kz0B8c_LICIqe6ghrESHeA5Cq_P/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YwkXZNFfvUYYEUpSrcB6zb3pIHdBRt-x/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1k0t2PySdG4-1uRspe6XFPJWeQrwNkCft/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pRl4p-nD6BNtvCAhuBxdJsKjz-z1lANO/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/157zCWopsVOjV85IGEMPclvVQEe0OXoY0/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cRxiThfr5JvTLBqgpyuXMUyNzzImw2fk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ax6BgIaoC0IE3NjCu4zArc8zvI2fNYHo/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1y3A3dEIXdSctgA0JDgvgkr3dEKX2nFdd/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MSIIC1yRK8prEFWYTEumq-ianD_7IJEW/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ONVdqjG0uCQtgDqxgvtSQexm3_CmlVSC/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A5KGgSDZZXTLHgSYStdbpjQ1azv-ycCV/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KTzfB3YjCtfiSvR7ABVFqqWGgQwNVs_d/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JmvU81JMYU3VyxL9eH_1VUYwsKhuKsPF/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n5Y5rpZA-5P6zzrD40yXAG5A2OzsifhS/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GpJkYe0vAc3kFPMTk90oQpJTucBRLIQm/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UWH7e5885MVzs9oQ9x53mDiVpVz1vOzq/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fdxiaAeaUD3UrGNpwkjrP4_EIU5EhxvF/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wtf3jdOGPzhoYAzQRAZSfX_Mn74-SUTq/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19mSP9RagtaWYafvv4KCl720FWsiwSwAJ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ei21D60-lqMYIDct-6DNZYBNq73wYg_m/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11gTC_5bdVJyuJ8pJXIQgw6MOOJqqv7vZ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gN6yoQLNk57mguWXG6EUMS5He-8lkJYn/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QnjuElRT2S2oUdET1e14q4md8RmNTBo3/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1orZ7JRKxKacrMKQUAFVC8h4p0spxETOG/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DxZfG5Su2vNVp8hbMU3IV-7jTtiEPbE_/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ArFDKljnbXLOmQSjUs4DWWvIqGt6hB3_/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1I4O1W9ouGoheUMl-rWYrezPOrhfWaYN8/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Yrigh9RDp6Zhr5NN6be-13Gx4Q_yj3J2/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ieUAvsFJC1vAYwGkBocg3dYbeMmzZsD_/view?usp=sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1206,13 +1209,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -1400,7 +1396,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1420,9 +1416,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1435,12 +1428,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1476,19 +1463,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1497,14 +1484,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1542,6 +1529,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1881,1326 +1871,1327 @@
   <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="11.5" style="32" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" style="32" customWidth="1"/>
-    <col min="4" max="4" width="26" style="8" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="8" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" style="8" customWidth="1"/>
-    <col min="9" max="14" width="10.83203125" style="8"/>
-    <col min="15" max="16" width="10.83203125" style="8" customWidth="1"/>
-    <col min="17" max="16384" width="10.83203125" style="8"/>
+    <col min="1" max="1" width="7.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="29" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="26" style="7" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" style="7" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="7"/>
+    <col min="15" max="16" width="10.83203125" style="7" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="30" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" s="27" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>195</v>
+      <c r="B2" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>196</v>
+      <c r="I2" s="1" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="107" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>47</v>
+      <c r="I3" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>55</v>
+      <c r="E4" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>196</v>
+        <v>32</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>197</v>
+      <c r="E5" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>205</v>
+      <c r="E6" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>71</v>
+        <v>32</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>204</v>
+      <c r="E7" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="147" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="D8" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="147" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="G8" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>34</v>
+      <c r="I8" s="32" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="218" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="155" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="155" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>82</v>
+      <c r="I10" s="32" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="164" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="10" t="s">
         <v>207</v>
       </c>
+      <c r="E11" s="9" t="s">
+        <v>178</v>
+      </c>
       <c r="F11" s="5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="222" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>89</v>
+      <c r="E12" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>92</v>
+      <c r="I12" s="32" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="163" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>95</v>
+        <v>86</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="32" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="166" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="166" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="166" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="D15" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="166" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>210</v>
+      <c r="I15" s="32" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>109</v>
+      <c r="E16" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>211</v>
+      <c r="I16" s="32" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>213</v>
+      <c r="E17" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>212</v>
+      <c r="I17" s="32" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D18" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>330</v>
+      <c r="E18" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>292</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>331</v>
+        <v>62</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="130" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>119</v>
+      <c r="E19" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>122</v>
+      <c r="I19" s="32" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D20" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>337</v>
+      <c r="E20" s="12" t="s">
+        <v>298</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>124</v>
+        <v>62</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="32" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>217</v>
+      <c r="I22" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="125" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>218</v>
+        <v>186</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>125</v>
+        <v>62</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="122" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>223</v>
+        <v>119</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>126</v>
+        <v>62</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="144" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>224</v>
+        <v>116</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="32" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="121" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I26" s="35" t="s">
+      <c r="H28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="124" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="121" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I28" s="35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="124" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>52</v>
+      <c r="E30" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>236</v>
+      <c r="I30" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>235</v>
+        <v>200</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>236</v>
+      <c r="I31" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>247</v>
+        <v>137</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>160</v>
+      <c r="I32" s="32" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="116" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>158</v>
+        <v>141</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>162</v>
+      <c r="I33" s="32" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>250</v>
+        <v>146</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>166</v>
+      <c r="I34" s="32" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="122" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>255</v>
+        <v>149</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>220</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I35" s="13" t="s">
-        <v>170</v>
+      <c r="I35" s="32" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="122" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>255</v>
+        <v>223</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>220</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>170</v>
+      <c r="I36" s="32" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="A37" s="8">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>174</v>
+        <v>153</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>154</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>260</v>
+      <c r="I37" s="32" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="A38" s="8">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>177</v>
+        <v>156</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>179</v>
+      <c r="I38" s="32" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="A39" s="8">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>261</v>
+      <c r="I39" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+      <c r="A40" s="8">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>262</v>
+        <v>160</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>183</v>
+      <c r="I40" s="32" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>185</v>
+        <v>227</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>187</v>
+        <v>62</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>263</v>
+        <v>166</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I42" s="13" t="s">
-        <v>191</v>
+      <c r="I42" s="32" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="107" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I43" s="35" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="107" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="107" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="G45" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>39</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I45" s="7" t="s">
-        <v>41</v>
+      <c r="I45" s="1" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -3251,6 +3242,7 @@
     <hyperlink ref="I3" r:id="rId41" xr:uid="{BF2741A9-F7F6-844F-BC80-937D356CC497}"/>
     <hyperlink ref="I2" r:id="rId42" xr:uid="{90FD387C-82BD-F041-AD1B-BF96637458AB}"/>
     <hyperlink ref="I31" r:id="rId43" xr:uid="{60433B83-9D69-374E-8FFE-A17EB0451B9F}"/>
+    <hyperlink ref="I36" r:id="rId44" xr:uid="{3F30084B-6236-E349-960D-8AA5F64618E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3262,181 +3254,181 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="76.83203125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>295</v>
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>275</v>
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
         <v>46032</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>276</v>
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>279</v>
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>198</v>
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>204</v>
+      <c r="A13" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="46"/>
-      <c r="B14" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>66</v>
+      <c r="A14" s="43"/>
+      <c r="B14" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>285</v>
+      <c r="A16" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47"/>
-      <c r="B17" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>285</v>
+      <c r="A17" s="44"/>
+      <c r="B17" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>288</v>
+      <c r="A18" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3461,182 +3453,182 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="67.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="79.5" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:4" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="35"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="43"/>
+      <c r="B14" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="44"/>
+      <c r="B17" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="37" t="s">
         <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="38"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="46"/>
-      <c r="B14" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47"/>
-      <c r="B17" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3661,190 +3653,190 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="88.5" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="37" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="17" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
+      <c r="C13" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>311</v>
-      </c>
     </row>
     <row r="14" spans="1:3" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>218</v>
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>222</v>
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>305</v>
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>305</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>288</v>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3869,189 +3861,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="69.83203125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
+      <c r="C13" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>315</v>
-      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>305</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="40"/>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4075,189 +4067,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
     <col min="3" max="3" width="69.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="18">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="21">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" t="s">
-        <v>319</v>
-      </c>
-    </row>
     <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>193</v>
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>265</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
       </c>
       <c r="C17" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="25"/>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4268,8 +4260,8 @@
     <mergeCell ref="A17:A18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{59185405-96EE-5545-9C2E-A79AD3D4E593}"/>
-    <hyperlink ref="C10" r:id="rId2" xr:uid="{8624B1E6-E90D-AE4C-B6E1-8F2EDB13E6FE}"/>
+    <hyperlink ref="C10" r:id="rId1" xr:uid="{8624B1E6-E90D-AE4C-B6E1-8F2EDB13E6FE}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{59185405-96EE-5545-9C2E-A79AD3D4E593}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4281,189 +4273,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="69.83203125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
+      <c r="C13" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>315</v>
-      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>315</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="40"/>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4487,189 +4479,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="69.83203125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
+      <c r="C13" s="35" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>327</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="40"/>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4693,189 +4685,189 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="69.83203125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="69.83203125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="34" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>270</v>
+    <row r="1" spans="1:3" s="31" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41"/>
+      <c r="B3" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="41"/>
+      <c r="B5" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="43"/>
+      <c r="B7" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43"/>
+      <c r="B9" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="46"/>
+      <c r="B12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46"/>
+      <c r="B13" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C2" s="38" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="17" t="s">
+      <c r="C13" s="35" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="43"/>
+      <c r="B15" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43"/>
+      <c r="B16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="39">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
-      <c r="B7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
-      <c r="B8" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
-      <c r="B9" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
-      <c r="B10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
-      <c r="B13" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="46"/>
-      <c r="B15" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="46"/>
-      <c r="B16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
-      <c r="B18" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>305</v>
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="40"/>
+      <c r="A19" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
